--- a/backtest_runs/20260410_193731/by_symbol/MEBL/MEBL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/MEBL/MEBL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-1229.730000000001</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>98770.27</v>
@@ -633,7 +633,7 @@
         <v>-2899.140000000006</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>101351.1</v>
@@ -679,7 +679,7 @@
         <v>-3760.179999999991</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>97590.92</v>
@@ -771,7 +771,7 @@
         <v>-1385.450000000003</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>104051.01</v>
@@ -817,7 +817,7 @@
         <v>-2109.089999999995</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>101941.92</v>
@@ -863,7 +863,7 @@
         <v>-632.0399999999979</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>101309.88</v>
@@ -909,7 +909,7 @@
         <v>-4818.160000000004</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>96491.72</v>
@@ -1047,7 +1047,7 @@
         <v>-1364.839999999995</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>99615.28</v>
@@ -1093,7 +1093,7 @@
         <v>-34.34999999999479</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>99580.93000000001</v>
@@ -1185,7 +1185,7 @@
         <v>-2425.109999999994</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>103320.5</v>
@@ -1277,7 +1277,7 @@
         <v>-4021.240000000001</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>100297.7</v>
@@ -1415,7 +1415,7 @@
         <v>-1316.75</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>107520.36</v>
@@ -1645,7 +1645,7 @@
         <v>-1708.339999999995</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>116620.82</v>
